--- a/Task Tracker.xlsx
+++ b/Task Tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/recep/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/recep/Desktop/digiMODE-unreal-cpp-internship-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE439C4-527A-DB47-B119-19CDF3C02A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDB1CF9-AE4F-454A-8A79-A0BFC094CEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="1660" windowWidth="31100" windowHeight="18160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Staj Takip" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="71">
   <si>
     <t>Görev</t>
   </si>
@@ -225,9 +225,6 @@
     <t>Claude</t>
   </si>
   <si>
-    <t>?%</t>
-  </si>
-  <si>
     <t xml:space="preserve">C++ Öğrenimi, Pointer Öğrenimi
 </t>
   </si>
@@ -248,6 +245,15 @@
   </si>
   <si>
     <t xml:space="preserve">UML Mimarisi Öğrenme </t>
+  </si>
+  <si>
+    <t>2 Hafta</t>
+  </si>
+  <si>
+    <t>C++ Genele mimarisi</t>
+  </si>
+  <si>
+    <t>C++'da Pointer yapısı</t>
   </si>
 </sst>
 </file>
@@ -950,13 +956,13 @@
         <v>46218</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L3" s="18" t="s">
         <v>58</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N3" s="23" t="s">
         <v>46</v>
@@ -979,11 +985,11 @@
       <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="24">
+        <v>0.01</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>61</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>62</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>41</v>
@@ -1005,13 +1011,13 @@
         <v>46223</v>
       </c>
       <c r="K4" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="M4" s="18" t="s">
         <v>64</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>65</v>
       </c>
       <c r="N4" s="23" t="s">
         <v>46</v>
@@ -1059,7 +1065,9 @@
       <c r="J5" s="21">
         <v>46219</v>
       </c>
-      <c r="K5" s="7"/>
+      <c r="K5" s="18" t="s">
+        <v>69</v>
+      </c>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="23" t="s">
@@ -1108,7 +1116,9 @@
       <c r="J6" s="21">
         <v>46220</v>
       </c>
-      <c r="K6" s="7"/>
+      <c r="K6" s="18" t="s">
+        <v>70</v>
+      </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="23" t="s">
@@ -1133,20 +1143,30 @@
         <v>18</v>
       </c>
       <c r="C7" s="6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="E7" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="9" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H7" s="21">
+        <v>46216</v>
+      </c>
+      <c r="I7" s="21">
+        <v>46223</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>45</v>
+      </c>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
@@ -1288,7 +1308,7 @@
     </row>
     <row r="11" spans="1:18" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>17</v>
